--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
@@ -816,7 +816,7 @@
   </si>
   <si>
     <t xml:space="preserve">打不开吗？
-…是啊，毕竟那个宝箱的锁是我精心设置的。
+…这样啊，毕竟那个宝箱的锁是我精心设置的。
 记住，就算带着开锁器，如果开锁技能太低也是打不开锁的。</t>
   </si>
   <si>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="fiama" sheetId="1" r:id="rId3"/>
+    <sheet name="fiama" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="165">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -671,187 +671,6 @@
     <t xml:space="preserve">I see... #last_choice...? That’s a very you kind of resolution.
 Hehe, speaking of which, I have something that’s just perfect for you. It's alright, do not hesitate.</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你看起来已经没事了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…你头上的伤还好吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">谢谢你救了我</t>
-  </si>
-  <si>
-    <t xml:space="preserve">丑陋野兽的故事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我有些事情想问你</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看来你已经决心在这片土地上生活了。
-为了祝贺你的新家园的发展，我会把我最重要的伙伴让给你一只。你喜欢什么样的动物？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狗！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">猫！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">熊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">少女！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的，要好好照顾它哦。
-如果和同伴失散的话，可以去附近城里的酒馆把它唤回来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给你的宠物伤痕累累地回到了我身边。
-…我应该跟你说过要好好照顾它吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">别客气。我只是做了理所当然的事情。
-在古老森林发现倒下的你时，我还以为你已经没救了。幸好你没事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在某个地方，有一个王子被魔法变成了丑陋的野兽。因为对自己的样貌感到绝望，于是他抛弃了国家跑到一处森林中的小屋生活。
-有一次，一个因为被狼袭击而受伤的女人跑进小屋晕倒了。王子不知如何是好，但还是选择了照顾女人。不过，女人也因为男人的模样吓哭了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">过了几天，女人发现男人非常温柔。他的坦诚打动了她的心。受伤后痊愈的女人决定要和男人一起生活。
-两人合力克服了各种困难。最后，王子的诅咒解除了，两人结婚后迎来了幸福的生活。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是哪里都能听到的故事。
-小时候赛特大人总会反反复复的给我讲这个故事，他说「故事的结局是悲伤的」。至今我也不知道他是如何看待这个人类创造的童话，又想通过这个童话向我传达什么…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么事？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古老森林？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾莱亚的力量是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">梦现之子是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(返回)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…在与提里斯隔海相望的东大陆上，有一片广袤深远的森林，艾莱亚就栖息在那片森林之中。人类绝不会踏入其中，因为森林的瘴气会夺走人类的理性，有时甚至会致死。那片森林的名字叫温戴尔，也被叫成异形之森。
-这片大陆上也还有一些像艾莱亚森林一样的古老森林…。虽然不至于像异形之森那样会夺走人的生命，但依然是很危险的地方。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果有不明白的事情就去问阿什。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你听说过住在异形森林的艾莱亚的「力量」吗？
-充满古老森林的蓝色瘴气也被称为「以太」，据说古代的艾莱亚编织了以太，这股力量足以撼动大地，呼风唤雨。我以为那只是传说…直到在尼米尔看到过赛特大人创造的奇迹，我才知道那都是真的。
-不知该说是幸运还是不幸，生活在森林外世界的艾莱亚们在很久以前就失去了那样的力量…不过…是除了「梦现之子」以外的艾莱亚们。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…艾莱亚的孩童之中可能会出现所谓的「梦现之子」。其实他们是患上了一种名叫梦现病的疾病。
-那些可怜的孩子在得了梦现病后会分不清梦境和现实，最终会陷入永无止境的沉眠。他们总是表情呆滞，像是心灵与外界完全隔离开来一样，会变得不在乎任何东西。
-梦现之子会在他们的梦中无意识的编织以太能量，如果这股力量失控就可能会在现实中引发难以预料的灾难。曾经有个笨蛋半开玩笑地去吓唬梦现之子，结果导致一整个村镇都被那股力量所摧毁。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目前还没有人找到能治疗梦现病的办法。梦现之子无论在哪里都是被忌讳的危险存在。于是人们就把他们送进古老森林，结束他们短暂的生命。
-…嗯，这是件会让人心情沉重的事。不过如果你要在米西利亚生活的话，就必须知道这件事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小时候，我很喜欢在古老森林玩耍。那时我还对赛特大人说「我可能真的是艾莱亚」，而他总会笑着听我这么说。
-在古老森林的大树下睡觉时，偶尔会做些不可思议的梦。梦里有充满蓝色光辉的河……我能感觉到那些水流很危险，但还是会无可奈何地被吸引过去。每当我想靠近河的时候，就会听到一个少女的声音告诉我说「不能去那里」。
-我觉得梦中少女的声音可能就是…不，不应该是那样的…对不起，尽跟你说了些不着边际的话。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你看到了我的梦吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…看来，你脑袋伤的很重啊。为了能好好休养，试着做张床怎么样？
-困的时候进行「冥想」也能睡着，不过，用床可以随时休息，疲劳恢复的效果也更好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，#pc_name#。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是吗，看来你还在做奇妙的梦呢
-确实梦中发生的事情和我的过去是一致的。
-那是我重要的记忆，你本不该知道的事情。
-我不知道为什么你会做那样的梦。或许你可以趁着还没忘记把梦里的事记录在日记上。你可以用这个…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其实我也不是讨厌人类，只是对我来说还是动物们更亲近一些。旅行的时候，我经常驯服各种动物。
-来这里之前也有一只可爱的小狗一直跟着我们。是一只好奇心旺盛的小家伙……不过在我们休息的时候，它好像又被什么吸引走了，然后就再也没有回来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">记得当时我们休息的地方附近有个洞窟。说不定那个孩子是在洞窟里迷路了。
-那洞窟不怎么危险，你能去找一下那只小狗吗？洞窟就在这里的西北方。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，果然是在洞穴里迷路了呢。还好你们都平安无事。
-谢谢你帮忙找到这只小狗。给你的谢礼也准备好了，请收下吧。
-波比，以后不要随便乱跑了，就让这个冒险家好好照顾你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你看起来已经习惯了这个地方的生活。我再教你一些会在今后生活中派的上用处的制造配方吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阿什说，让我委托你探索洞窟。
-尼米尔…是一个被称为风之墓地的洞窟。从几年前开始那里就有很多发现异变的报告。我也能感受到，那个洞窟深处确实发生了些什么。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不知道会有怎样的危险在等着，请你一定要小心。
-愿你得到风的加护，#pc。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在你前往尼米尔之前，我想告诉你一件事。
-地城中有些宝箱是被锁住的，开锁时需要一种叫做「开锁器」的工具。我在你脚下放了一个锁着的宝箱，你可以试着用这开锁器打开。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">打不开吗？
-…这样啊，毕竟那个宝箱的锁是我精心设置的。
-记住，就算带着开锁器，如果开锁技能太低也是打不开锁的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那个宝箱和开锁器就送给你了。当你成为独当一面的冒险家时，里面的东西一定对你有用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真快啊，我们在这片原野上相遇后，已经过了一周了。
-阿什看起来也很开心……真的很感谢你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然最初有些担忧，但是现在，看来你已经可以在这片土地生活了。你大概也有将来的目标了吧？
-我一直想问你，你今后打算做什么呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想探索奈菲亚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想发展据点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想去各种各样的地方看看</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做些不可告人的事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么都不想做</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想死</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样啊…「#last_choice」…。这目标很有你的风格。
-呵呵，说起来，我正好有适合你的东西。不用客气，收下吧。</t>
-  </si>
 </sst>
 </file>
 
@@ -871,19 +690,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -896,7 +715,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -929,7 +748,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -938,62 +757,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1007,13 +826,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1189,25 +1008,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K159"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,23 +1061,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1266,7 +1085,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1274,16 +1093,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1292,15 +1111,12 @@
       <c r="J12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1309,11 +1125,8 @@
       <c r="J13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1323,7 +1136,7 @@
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1332,11 +1145,8 @@
       <c r="J16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1346,7 +1156,7 @@
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1355,18 +1165,15 @@
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1375,11 +1182,8 @@
       <c r="J18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1387,22 +1191,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1410,7 +1214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
         <v>41</v>
       </c>
@@ -1418,8 +1222,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" ht="53.7">
-      <c r="H26" s="1">
+    <row r="26" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -1428,18 +1232,15 @@
       <c r="J26" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1448,18 +1249,15 @@
       <c r="J27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1468,18 +1266,15 @@
       <c r="J28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -1488,18 +1283,15 @@
       <c r="J29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" ht="12.8">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -1508,11 +1300,8 @@
       <c r="J30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -1523,12 +1312,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -1539,12 +1328,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -1555,12 +1344,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
@@ -1571,18 +1360,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" ht="12.8">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" ht="43.25">
-      <c r="H43" s="1">
+    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -1591,11 +1380,8 @@
       <c r="J43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
         <v>12</v>
       </c>
@@ -1603,13 +1389,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" ht="43.25">
-      <c r="H47" s="1">
+    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="1" t="n">
         <v>40</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -1618,11 +1404,8 @@
       <c r="J47" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" ht="12.8">
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="1" t="s">
         <v>57</v>
       </c>
@@ -1630,18 +1413,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" ht="43.25">
-      <c r="H51" s="1">
+    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -1650,22 +1433,19 @@
       <c r="J51" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K51" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" ht="12.8">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" ht="12.8">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="56" ht="85.05">
-      <c r="H56" s="1">
+    <row r="56" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -1674,12 +1454,9 @@
       <c r="J56" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K56" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="57" ht="85.05">
-      <c r="H57" s="1">
+    </row>
+    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
@@ -1688,12 +1465,9 @@
       <c r="J57" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K57" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" ht="64.15">
-      <c r="H58" s="1">
+    </row>
+    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H58" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -1702,20 +1476,17 @@
       <c r="J58" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="K58" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="59" ht="12.8">
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" ht="12.8">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1724,18 +1495,15 @@
       <c r="J61" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K61" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" ht="12.8">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -1744,11 +1512,8 @@
       <c r="J62" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" ht="12.8">
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
         <v>84</v>
       </c>
@@ -1758,7 +1523,7 @@
       <c r="D63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -1767,11 +1532,8 @@
       <c r="J63" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K63" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="64" ht="12.8">
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="1" t="s">
         <v>88</v>
       </c>
@@ -1781,7 +1543,7 @@
       <c r="D64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -1790,18 +1552,15 @@
       <c r="J64" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K64" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="65" ht="12.8">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -1810,11 +1569,8 @@
       <c r="J65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K65" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" ht="12.8">
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="s">
         <v>17</v>
       </c>
@@ -1822,13 +1578,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="70" ht="116.4">
-      <c r="H70" s="1">
+    <row r="70" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I70" s="4" t="s">
@@ -1837,23 +1593,20 @@
       <c r="J70" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K70" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" ht="12.8">
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" ht="12.8">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -1862,17 +1615,14 @@
       <c r="J74" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K74" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="79" ht="12.8">
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="80" ht="137.3">
-      <c r="H80" s="1">
+    <row r="80" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -1881,22 +1631,19 @@
       <c r="J80" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="K80" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="81" ht="12.8">
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="83" ht="12.8">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="84" ht="147.75">
-      <c r="H84" s="1">
+    <row r="84" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H84" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -1905,12 +1652,9 @@
       <c r="J84" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="K84" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" ht="85.05">
-      <c r="H85" s="1">
+    </row>
+    <row r="85" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -1919,12 +1663,9 @@
       <c r="J85" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="K85" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="86" ht="12.8">
-      <c r="H86" s="1">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H86" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -1933,12 +1674,9 @@
       <c r="J86" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="K86" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="87" ht="147.75">
-      <c r="H87" s="1">
+    </row>
+    <row r="87" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H87" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I87" s="4" t="s">
@@ -1947,22 +1685,19 @@
       <c r="J87" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K87" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="88" ht="12.8">
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="90" ht="12.8">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="91" ht="12.8">
-      <c r="H91" s="1">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -1971,33 +1706,27 @@
       <c r="J91" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K91" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="92" ht="74.6">
-      <c r="H92" s="1">
+    </row>
+    <row r="92" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K92" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="93" ht="12.8">
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D93" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="96" ht="12.8">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" ht="12.8">
-      <c r="H97" s="1">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H97" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -2006,33 +1735,27 @@
       <c r="J97" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="98" ht="95.5">
-      <c r="H98" s="1">
+    </row>
+    <row r="98" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H98" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="K98" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="99" ht="12.8">
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D99" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="101" ht="12.8">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="102" ht="113.4">
-      <c r="H102" s="1">
+    <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I102" s="5" t="s">
@@ -2041,12 +1764,9 @@
       <c r="J102" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="K102" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="103" ht="79.85">
-      <c r="H103" s="1">
+    </row>
+    <row r="103" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H103" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I103" s="5" t="s">
@@ -2055,11 +1775,8 @@
       <c r="J103" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K103" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="104" ht="12.8">
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="1" t="s">
         <v>121</v>
       </c>
@@ -2067,18 +1784,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" ht="12.8">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="108" ht="12.8">
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="109" ht="91">
-      <c r="H109" s="1">
+    <row r="109" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H109" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I109" s="5" t="s">
@@ -2087,26 +1804,23 @@
       <c r="J109" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="K109" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="111" ht="12.8">
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="112" ht="12.8">
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="115" ht="12.8">
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="116" ht="12.8">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="1" t="s">
         <v>121</v>
       </c>
@@ -2114,9 +1828,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="117" ht="13.8">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E117" s="6"/>
-      <c r="H117" s="1">
+      <c r="H117" s="1" t="n">
         <v>34</v>
       </c>
       <c r="I117" s="7" t="s">
@@ -2125,12 +1839,9 @@
       <c r="J117" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K117" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="118" ht="79.85">
-      <c r="H118" s="1">
+    </row>
+    <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H118" s="1" t="n">
         <v>35</v>
       </c>
       <c r="I118" s="5" t="s">
@@ -2139,12 +1850,9 @@
       <c r="J118" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K118" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="119" ht="46.25">
-      <c r="H119" s="1">
+    </row>
+    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H119" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I119" s="5" t="s">
@@ -2153,31 +1861,28 @@
       <c r="J119" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="K119" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="120" ht="12.8">
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="121" ht="12.8">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="124" ht="12.8">
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="125" ht="12.8">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E125" s="6"/>
     </row>
-    <row r="126" ht="91">
+    <row r="126" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E126" s="6"/>
-      <c r="H126" s="1">
+      <c r="H126" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I126" s="5" t="s">
@@ -2186,11 +1891,8 @@
       <c r="J126" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="K126" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="127" ht="12.8">
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="1" t="s">
         <v>121</v>
       </c>
@@ -2198,22 +1900,22 @@
         <v>138</v>
       </c>
     </row>
-    <row r="128" ht="12.8">
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="130" ht="12.8">
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E131" s="6"/>
     </row>
-    <row r="132" ht="91">
+    <row r="132" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E132" s="6"/>
-      <c r="H132" s="1">
+      <c r="H132" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I132" s="5" t="s">
@@ -2222,12 +1924,9 @@
       <c r="J132" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="K132" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="133" ht="35.05">
-      <c r="H133" s="1">
+    </row>
+    <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H133" s="1" t="n">
         <v>39</v>
       </c>
       <c r="I133" s="5" t="s">
@@ -2236,26 +1935,23 @@
       <c r="J133" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="K133" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="134" ht="12.8">
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D134" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="135" ht="12.8">
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D135" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="140" ht="12.8">
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="142" ht="12.8">
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D142" s="1" t="s">
         <v>121</v>
       </c>
@@ -2263,8 +1959,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" ht="57.45">
-      <c r="H145" s="1">
+    <row r="145" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H145" s="1" t="n">
         <v>41</v>
       </c>
       <c r="I145" s="5" t="s">
@@ -2273,12 +1969,9 @@
       <c r="J145" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K145" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="146" ht="68.65">
-      <c r="H146" s="1">
+    </row>
+    <row r="146" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H146" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I146" s="5" t="s">
@@ -2287,18 +1980,15 @@
       <c r="J146" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="K146" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="147" ht="13.8">
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H147" s="1">
+      <c r="H147" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I147" s="5" t="s">
@@ -2307,18 +1997,15 @@
       <c r="J147" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K147" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="148" ht="13.8">
+    </row>
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H148" s="1">
+      <c r="H148" s="1" t="n">
         <v>44</v>
       </c>
       <c r="I148" s="5" t="s">
@@ -2327,18 +2014,15 @@
       <c r="J148" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="K148" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="149" ht="13.8">
+    </row>
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H149" s="1">
+      <c r="H149" s="1" t="n">
         <v>45</v>
       </c>
       <c r="I149" s="5" t="s">
@@ -2347,11 +2031,8 @@
       <c r="J149" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="K149" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="150" ht="13.8">
+    </row>
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
         <v>150</v>
       </c>
@@ -2359,7 +2040,7 @@
         <v>26</v>
       </c>
       <c r="G150" s="4"/>
-      <c r="H150" s="1">
+      <c r="H150" s="1" t="n">
         <v>46</v>
       </c>
       <c r="I150" s="5" t="s">
@@ -2368,18 +2049,15 @@
       <c r="J150" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="K150" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="151" ht="13.8">
+    </row>
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H151" s="1" t="n">
         <v>47</v>
       </c>
       <c r="I151" s="5" t="s">
@@ -2388,18 +2066,15 @@
       <c r="J151" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="K151" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="152" ht="13.8">
+    </row>
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H152" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I152" s="5" t="s">
@@ -2408,25 +2083,22 @@
       <c r="J152" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K152" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="153" ht="13.8">
+    </row>
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I153" s="5"/>
       <c r="J153" s="4"/>
     </row>
-    <row r="154" ht="12.8">
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I154" s="4"/>
     </row>
-    <row r="155" ht="12.8">
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I155" s="4"/>
     </row>
-    <row r="156" ht="57.45">
-      <c r="H156" s="1">
+    <row r="156" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H156" s="1" t="n">
         <v>49</v>
       </c>
       <c r="I156" s="5" t="s">
@@ -2435,11 +2107,8 @@
       <c r="J156" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="K156" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="157" ht="12.8">
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D157" s="1" t="s">
         <v>57</v>
       </c>
@@ -2447,24 +2116,24 @@
         <v>145</v>
       </c>
     </row>
-    <row r="158" ht="12.8">
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D158" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="159" ht="12.8">
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D159" s="1" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fiama.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="fiama" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fiama" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="215">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -671,6 +671,187 @@
     <t xml:space="preserve">I see... #last_choice...? That’s a very you kind of resolution.
 Hehe, speaking of which, I have something that’s just perfect for you. It's alright, do not hesitate.</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你看起来已经没事了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…你头上的伤还好吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">谢谢你救了我</t>
+  </si>
+  <si>
+    <t xml:space="preserve">丑陋野兽的故事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我有些事情想问你</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看来你已经决心在这片土地上生活了。
+为了祝贺你的新家园的发展，我会把我最重要的伙伴让给你一只。你喜欢什么样的动物？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狗！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">猫！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">熊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少女！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，要好好照顾它哦。
+如果和同伴失散的话，可以去附近城里的酒馆把它唤回来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给你的宠物伤痕累累地回到了我身边。
+…我应该跟你说过要好好照顾它吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别客气。我只是做了理所当然的事情。
+在古老森林发现倒下的你时，我还以为你已经没救了。幸好你没事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在某个地方，有一个王子被魔法变成了丑陋的野兽。因为对自己的样貌感到绝望，于是他抛弃了国家跑到一处森林中的小屋生活。
+有一次，一个因为被狼袭击而受伤的女人跑进小屋晕倒了。王子不知如何是好，但还是选择了照顾女人。不过，女人也因为男人的模样吓哭了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">过了几天，女人发现男人非常温柔。他的坦诚打动了她的心。受伤后痊愈的女人决定要和男人一起生活。
+两人合力克服了各种困难。最后，王子的诅咒解除了，两人结婚后迎来了幸福的生活。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是哪里都能听到的故事。
+小时候赛特大人总会反反复复的给我讲这个故事，他说「故事的结局是悲伤的」。至今我也不知道他是如何看待这个人类创造的童话，又想通过这个童话向我传达什么…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么事？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古老森林？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾莱亚的力量是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">梦现之子是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(返回)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…在与提里斯隔海相望的东大陆上，有一片广袤深远的森林，艾莱亚就栖息在那片森林之中。人类绝不会踏入其中，因为森林的瘴气会夺走人类的理性，有时甚至会致死。那片森林的名字叫温戴尔，也被叫成异形之森。
+这片大陆上也还有一些像艾莱亚森林一样的古老森林…。虽然不至于像异形之森那样会夺走人的生命，但依然是很危险的地方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果有不明白的事情就去问阿什。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你听说过住在异形森林的艾莱亚的「力量」吗？
+充满古老森林的蓝色瘴气也被称为「以太」，据说古代的艾莱亚编织了以太，这股力量足以撼动大地，呼风唤雨。我以为那只是传说…直到在尼米尔看到过赛特大人创造的奇迹，我才知道那都是真的。
+不知该说是幸运还是不幸，生活在森林外世界的艾莱亚们在很久以前就失去了那样的力量…不过…是除了「梦现之子」以外的艾莱亚们。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…艾莱亚的孩童之中可能会出现所谓的「梦现之子」。其实他们是患上了一种名叫梦现病的疾病。
+那些可怜的孩子在得了梦现病后会分不清梦境和现实，最终会陷入永无止境的沉眠。他们总是表情呆滞，像是心灵与外界完全隔离开来一样，会变得不在乎任何东西。
+梦现之子会在他们的梦中无意识的编织以太能量，如果这股力量失控就可能会在现实中引发难以预料的灾难。曾经有个笨蛋半开玩笑地去吓唬梦现之子，结果导致一整个村镇都被那股力量所摧毁。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前还没有人找到能治疗梦现病的办法。梦现之子无论在哪里都是被忌讳的危险存在。于是人们就把他们送进古老森林，结束他们短暂的生命。
+…嗯，这是件会让人心情沉重的事。不过如果你要在米西利亚生活的话，就必须知道这件事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小时候，我很喜欢在古老森林玩耍。那时我还对赛特大人说「我可能真的是艾莱亚」，而他总会笑着听我这么说。
+在古老森林的大树下睡觉时，偶尔会做些不可思议的梦。梦里有充满蓝色光辉的河……我能感觉到那些水流很危险，但还是会无可奈何地被吸引过去。每当我想靠近河的时候，就会听到一个少女的声音告诉我说「不能去那里」。
+我觉得梦中少女的声音可能就是…不，不应该是那样的…对不起，尽跟你说了些不着边际的话。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你看到了我的梦吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…看来，你脑袋伤的很重啊。为了能好好休养，试着做张床怎么样？
+困的时候进行「冥想」也能睡着，不过，用床可以随时休息，疲劳恢复的效果也更好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，#pc_name#。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是吗，看来你还在做奇妙的梦呢
+确实梦中发生的事情和我的过去是一致的。
+那是我重要的记忆，你本不该知道的事情。
+我不知道为什么你会做那样的梦。或许你可以趁着还没忘记把梦里的事记录在日记上。你可以用这个…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其实我也不是讨厌人类，只是对我来说还是动物们更亲近一些。旅行的时候，我经常驯服各种动物。
+来这里之前也有一只可爱的小狗一直跟着我们。是一只好奇心旺盛的小家伙……不过在我们休息的时候，它好像又被什么吸引走了，然后就再也没有回来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">记得当时我们休息的地方附近有个洞窟。说不定那个孩子是在洞窟里迷路了。
+那洞窟不怎么危险，你能去找一下那只小狗吗？洞窟就在这里的西北方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，果然是在洞穴里迷路了呢。还好你们都平安无事。
+谢谢你帮忙找到这只小狗。给你的谢礼也准备好了，请收下吧。
+波比，以后不要随便乱跑了，就让这个冒险家好好照顾你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你看起来已经习惯了这个地方的生活。我再教你一些会在今后生活中派的上用处的制造配方吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿什说，让我委托你探索洞窟。
+尼米尔…是一个被称为风之墓地的洞窟。从几年前开始那里就有很多发现异变的报告。我也能感受到，那个洞窟深处确实发生了些什么。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不知道会有怎样的危险在等着，请你一定要小心。
+愿你得到风的加护，#pc。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在你前往尼米尔之前，我想告诉你一件事。
+地城中有些宝箱是被锁住的，开锁时需要一种叫做「开锁器」的工具。我在你脚下放了一个锁着的宝箱，你可以试着用这开锁器打开。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打不开吗？
+…这样啊，毕竟那个宝箱的锁是我精心设置的。
+记住，就算带着开锁器，如果开锁技能太低也是打不开锁的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那个宝箱和开锁器就送给你了。当你成为独当一面的冒险家时，里面的东西一定对你有用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真快啊，我们在这片原野上相遇后，已经过了一周了。
+阿什看起来也很开心……真的很感谢你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然最初有些担忧，但是现在，看来你已经可以在这片土地生活了。你大概也有将来的目标了吧？
+我一直想问你，你今后打算做什么呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想探索奈菲亚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想发展据点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想去各种各样的地方看看</t>
+  </si>
+  <si>
+    <t xml:space="preserve">做些不可告人的事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么都不想做</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想死</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这样啊…「#last_choice」…。这目标很有你的风格。
+呵呵，说起来，我正好有适合你的东西。不用客气，收下吧。</t>
+  </si>
 </sst>
 </file>
 
@@ -690,19 +871,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -715,7 +896,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -748,7 +929,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -757,62 +938,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -826,13 +1007,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1008,25 +1189,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K159"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,23 +1242,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1085,7 +1266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1093,16 +1274,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="1">
         <v>50</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1111,12 +1292,15 @@
       <c r="J12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="1">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1125,8 +1309,11 @@
       <c r="J13" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1136,7 +1323,7 @@
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="1">
         <v>2</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1145,8 +1332,11 @@
       <c r="J16" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1156,7 +1346,7 @@
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="1">
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1165,15 +1355,18 @@
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="1">
         <v>4</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1182,8 +1375,11 @@
       <c r="J18" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1191,22 +1387,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1214,7 +1410,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="D25" s="1" t="s">
         <v>41</v>
       </c>
@@ -1222,8 +1418,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="1" t="n">
+    <row r="26" ht="53.7">
+      <c r="H26" s="1">
         <v>5</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -1232,15 +1428,18 @@
       <c r="J26" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="1">
         <v>6</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1249,15 +1448,18 @@
       <c r="J27" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="B28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="1">
         <v>7</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1266,15 +1468,18 @@
       <c r="J28" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="1">
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -1283,15 +1488,18 @@
       <c r="J29" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="1">
         <v>9</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -1300,8 +1508,11 @@
       <c r="J30" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -1312,12 +1523,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="B33" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -1328,12 +1539,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="B35" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -1344,12 +1555,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="B37" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
@@ -1360,18 +1571,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="B39" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="12.8">
       <c r="A42" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H43" s="1" t="n">
+    <row r="43" ht="43.25">
+      <c r="H43" s="1">
         <v>10</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -1380,8 +1591,11 @@
       <c r="J43" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="B44" s="1" t="s">
         <v>12</v>
       </c>
@@ -1389,13 +1603,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H47" s="1" t="n">
+    <row r="47" ht="43.25">
+      <c r="H47" s="1">
         <v>40</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -1404,8 +1618,11 @@
       <c r="J47" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" ht="12.8">
       <c r="D48" s="1" t="s">
         <v>57</v>
       </c>
@@ -1413,18 +1630,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="D49" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="A50" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H51" s="1" t="n">
+    <row r="51" ht="43.25">
+      <c r="H51" s="1">
         <v>11</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -1433,19 +1650,22 @@
       <c r="J51" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" ht="12.8">
       <c r="B52" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="12.8">
       <c r="A55" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H56" s="1" t="n">
+    <row r="56" ht="85.05">
+      <c r="H56" s="1">
         <v>12</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -1454,9 +1674,12 @@
       <c r="J56" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H57" s="1" t="n">
+      <c r="K56" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="57" ht="85.05">
+      <c r="H57" s="1">
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
@@ -1465,9 +1688,12 @@
       <c r="J57" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H58" s="1" t="n">
+      <c r="K57" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" ht="64.15">
+      <c r="H58" s="1">
         <v>14</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -1476,17 +1702,20 @@
       <c r="J58" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" ht="12.8">
       <c r="B59" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.8">
       <c r="A61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="H61" s="1">
         <v>15</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1495,15 +1724,18 @@
       <c r="J61" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" ht="12.8">
       <c r="B62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="H62" s="1">
         <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -1512,8 +1744,11 @@
       <c r="J62" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
         <v>84</v>
       </c>
@@ -1523,7 +1758,7 @@
       <c r="D63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H63" s="1" t="n">
+      <c r="H63" s="1">
         <v>17</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -1532,8 +1767,11 @@
       <c r="J63" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K63" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" ht="12.8">
       <c r="B64" s="1" t="s">
         <v>88</v>
       </c>
@@ -1543,7 +1781,7 @@
       <c r="D64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="1">
         <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -1552,15 +1790,18 @@
       <c r="J64" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65" ht="12.8">
       <c r="B65" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="1" t="n">
+      <c r="H65" s="1">
         <v>19</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -1569,8 +1810,11 @@
       <c r="J65" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="66" ht="12.8">
       <c r="B66" s="1" t="s">
         <v>17</v>
       </c>
@@ -1578,13 +1822,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="A69" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H70" s="1" t="n">
+    <row r="70" ht="116.4">
+      <c r="H70" s="1">
         <v>20</v>
       </c>
       <c r="I70" s="4" t="s">
@@ -1593,20 +1837,23 @@
       <c r="J70" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" ht="12.8">
       <c r="B71" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="D74" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="H74" s="1">
         <v>21</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -1615,14 +1862,17 @@
       <c r="J74" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" ht="12.8">
       <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="1" t="n">
+    <row r="80" ht="137.3">
+      <c r="H80" s="1">
         <v>22</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -1631,19 +1881,22 @@
       <c r="J80" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" ht="12.8">
       <c r="B81" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="12.8">
       <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H84" s="1" t="n">
+    <row r="84" ht="147.75">
+      <c r="H84" s="1">
         <v>23</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -1652,9 +1905,12 @@
       <c r="J84" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H85" s="1" t="n">
+      <c r="K84" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" ht="85.05">
+      <c r="H85" s="1">
         <v>24</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -1663,9 +1919,12 @@
       <c r="J85" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H86" s="1" t="n">
+      <c r="K85" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
+      <c r="H86" s="1">
         <v>25</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -1674,9 +1933,12 @@
       <c r="J86" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H87" s="1" t="n">
+      <c r="K86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" ht="147.75">
+      <c r="H87" s="1">
         <v>26</v>
       </c>
       <c r="I87" s="4" t="s">
@@ -1685,19 +1947,22 @@
       <c r="J87" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K87" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" ht="12.8">
       <c r="B88" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="12.8">
       <c r="A90" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H91" s="1" t="n">
+    <row r="91" ht="12.8">
+      <c r="H91" s="1">
         <v>27</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -1706,27 +1971,33 @@
       <c r="J91" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H92" s="1" t="n">
+      <c r="K91" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="92" ht="74.6">
+      <c r="H92" s="1">
         <v>28</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K92" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" ht="12.8">
       <c r="D93" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="12.8">
       <c r="A96" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H97" s="1" t="n">
+    <row r="97" ht="12.8">
+      <c r="H97" s="1">
         <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -1735,27 +2006,33 @@
       <c r="J97" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H98" s="1" t="n">
+      <c r="K97" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" ht="95.5">
+      <c r="H98" s="1">
         <v>30</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" ht="12.8">
       <c r="D99" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.8">
       <c r="A101" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H102" s="1" t="n">
+    <row r="102" ht="113.4">
+      <c r="H102" s="1">
         <v>31</v>
       </c>
       <c r="I102" s="5" t="s">
@@ -1764,9 +2041,12 @@
       <c r="J102" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H103" s="1" t="n">
+      <c r="K102" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" ht="79.85">
+      <c r="H103" s="1">
         <v>33</v>
       </c>
       <c r="I103" s="5" t="s">
@@ -1775,8 +2055,11 @@
       <c r="J103" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K103" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104" ht="12.8">
       <c r="D104" s="1" t="s">
         <v>121</v>
       </c>
@@ -1784,18 +2067,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="12.8">
       <c r="D105" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" ht="12.8">
       <c r="A108" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H109" s="1" t="n">
+    <row r="109" ht="91">
+      <c r="H109" s="1">
         <v>32</v>
       </c>
       <c r="I109" s="5" t="s">
@@ -1804,23 +2087,26 @@
       <c r="J109" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K109" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="111" ht="12.8">
       <c r="D111" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" ht="12.8">
       <c r="D112" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" ht="12.8">
       <c r="A115" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="12.8">
       <c r="D116" s="1" t="s">
         <v>121</v>
       </c>
@@ -1828,9 +2114,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" ht="13.8">
       <c r="E117" s="6"/>
-      <c r="H117" s="1" t="n">
+      <c r="H117" s="1">
         <v>34</v>
       </c>
       <c r="I117" s="7" t="s">
@@ -1839,9 +2125,12 @@
       <c r="J117" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H118" s="1" t="n">
+      <c r="K117" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" ht="79.85">
+      <c r="H118" s="1">
         <v>35</v>
       </c>
       <c r="I118" s="5" t="s">
@@ -1850,9 +2139,12 @@
       <c r="J118" s="4" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H119" s="1" t="n">
+      <c r="K118" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="119" ht="46.25">
+      <c r="H119" s="1">
         <v>36</v>
       </c>
       <c r="I119" s="5" t="s">
@@ -1861,28 +2153,31 @@
       <c r="J119" s="4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K119" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="120" ht="12.8">
       <c r="D120" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="12.8">
       <c r="D121" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" ht="12.8">
       <c r="A124" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="12.8">
       <c r="E125" s="6"/>
     </row>
-    <row r="126" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" ht="91">
       <c r="E126" s="6"/>
-      <c r="H126" s="1" t="n">
+      <c r="H126" s="1">
         <v>37</v>
       </c>
       <c r="I126" s="5" t="s">
@@ -1891,8 +2186,11 @@
       <c r="J126" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K126" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="127" ht="12.8">
       <c r="D127" s="1" t="s">
         <v>121</v>
       </c>
@@ -1900,22 +2198,22 @@
         <v>138</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" ht="12.8">
       <c r="D128" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" ht="12.8">
       <c r="A130" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
       <c r="E131" s="6"/>
     </row>
-    <row r="132" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="91">
       <c r="E132" s="6"/>
-      <c r="H132" s="1" t="n">
+      <c r="H132" s="1">
         <v>38</v>
       </c>
       <c r="I132" s="5" t="s">
@@ -1924,9 +2222,12 @@
       <c r="J132" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H133" s="1" t="n">
+      <c r="K132" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="133" ht="35.05">
+      <c r="H133" s="1">
         <v>39</v>
       </c>
       <c r="I133" s="5" t="s">
@@ -1935,23 +2236,26 @@
       <c r="J133" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K133" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="134" ht="12.8">
       <c r="D134" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" ht="12.8">
       <c r="D135" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="12.8">
       <c r="A140" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" ht="12.8">
       <c r="D142" s="1" t="s">
         <v>121</v>
       </c>
@@ -1959,8 +2263,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H145" s="1" t="n">
+    <row r="145" ht="57.45">
+      <c r="H145" s="1">
         <v>41</v>
       </c>
       <c r="I145" s="5" t="s">
@@ -1969,9 +2273,12 @@
       <c r="J145" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H146" s="1" t="n">
+      <c r="K145" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="146" ht="68.65">
+      <c r="H146" s="1">
         <v>42</v>
       </c>
       <c r="I146" s="5" t="s">
@@ -1980,15 +2287,18 @@
       <c r="J146" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K146" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="147" ht="13.8">
       <c r="A147" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H147" s="1" t="n">
+      <c r="H147" s="1">
         <v>43</v>
       </c>
       <c r="I147" s="5" t="s">
@@ -1997,15 +2307,18 @@
       <c r="J147" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K147" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="148" ht="13.8">
       <c r="A148" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="H148" s="1">
         <v>44</v>
       </c>
       <c r="I148" s="5" t="s">
@@ -2014,15 +2327,18 @@
       <c r="J148" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K148" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="149" ht="13.8">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H149" s="1" t="n">
+      <c r="H149" s="1">
         <v>45</v>
       </c>
       <c r="I149" s="5" t="s">
@@ -2031,8 +2347,11 @@
       <c r="J149" s="4" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K149" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="150" ht="13.8">
       <c r="A150" s="1" t="s">
         <v>150</v>
       </c>
@@ -2040,7 +2359,7 @@
         <v>26</v>
       </c>
       <c r="G150" s="4"/>
-      <c r="H150" s="1" t="n">
+      <c r="H150" s="1">
         <v>46</v>
       </c>
       <c r="I150" s="5" t="s">
@@ -2049,15 +2368,18 @@
       <c r="J150" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K150" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="151" ht="13.8">
       <c r="A151" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="H151" s="1">
         <v>47</v>
       </c>
       <c r="I151" s="5" t="s">
@@ -2066,15 +2388,18 @@
       <c r="J151" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K151" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="152" ht="13.8">
       <c r="A152" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H152" s="1" t="n">
+      <c r="H152" s="1">
         <v>48</v>
       </c>
       <c r="I152" s="5" t="s">
@@ -2083,22 +2408,25 @@
       <c r="J152" s="4" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K152" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="153" ht="13.8">
       <c r="I153" s="5"/>
       <c r="J153" s="4"/>
     </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" ht="12.8">
       <c r="A154" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I154" s="4"/>
     </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" ht="12.8">
       <c r="I155" s="4"/>
     </row>
-    <row r="156" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H156" s="1" t="n">
+    <row r="156" ht="57.45">
+      <c r="H156" s="1">
         <v>49</v>
       </c>
       <c r="I156" s="5" t="s">
@@ -2107,8 +2435,11 @@
       <c r="J156" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K156" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="157" ht="12.8">
       <c r="D157" s="1" t="s">
         <v>57</v>
       </c>
@@ -2116,24 +2447,24 @@
         <v>145</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" ht="12.8">
       <c r="D158" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="12.8">
       <c r="D159" s="1" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
